--- a/artfynd/A 33107-2026 artfynd.xlsx
+++ b/artfynd/A 33107-2026 artfynd.xlsx
@@ -3259,7 +3259,7 @@
         <v>137251189</v>
       </c>
       <c r="B25" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>137251064</v>
       </c>
       <c r="B32" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>137251140</v>
       </c>
       <c r="B33" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>137251174</v>
       </c>
       <c r="B34" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>137251127</v>
       </c>
       <c r="B35" t="n">
-        <v>92067</v>
+        <v>92070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137251110</v>
       </c>
       <c r="B37" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137251111</v>
       </c>
       <c r="B38" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>137251047</v>
       </c>
       <c r="B191" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>137251102</v>
       </c>
       <c r="B192" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>137251109</v>
       </c>
       <c r="B193" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>137251122</v>
       </c>
       <c r="B194" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>137251154</v>
       </c>
       <c r="B195" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 33107-2026 artfynd.xlsx
+++ b/artfynd/A 33107-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137251049</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137251059</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137251068</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137251072</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137251078</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137251079</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137251084</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137251090</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137251100</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137251108</v>
       </c>
       <c r="B13" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137251114</v>
       </c>
       <c r="B14" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137251116</v>
       </c>
       <c r="B15" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137251117</v>
       </c>
       <c r="B16" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137251134</v>
       </c>
       <c r="B17" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137251135</v>
       </c>
       <c r="B18" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137251136</v>
       </c>
       <c r="B19" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137251146</v>
       </c>
       <c r="B20" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137251148</v>
       </c>
       <c r="B21" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137251192</v>
       </c>
       <c r="B22" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137251194</v>
       </c>
       <c r="B23" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137251197</v>
       </c>
       <c r="B24" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137251189</v>
       </c>
       <c r="B25" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137251099</v>
       </c>
       <c r="B27" t="n">
-        <v>79598</v>
+        <v>79608</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>137251060</v>
       </c>
       <c r="B29" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>137251063</v>
       </c>
       <c r="B30" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>137251064</v>
       </c>
       <c r="B32" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>137251140</v>
       </c>
       <c r="B33" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>137251174</v>
       </c>
       <c r="B34" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>137251127</v>
       </c>
       <c r="B35" t="n">
-        <v>92070</v>
+        <v>92080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>137249391</v>
       </c>
       <c r="B36" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137251110</v>
       </c>
       <c r="B37" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137251111</v>
       </c>
       <c r="B38" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>137247320</v>
       </c>
       <c r="B49" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>137247343</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>137247420</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137247486</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>137247513</v>
       </c>
       <c r="B53" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>137247625</v>
       </c>
       <c r="B54" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>137247711</v>
       </c>
       <c r="B55" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>137247798</v>
       </c>
       <c r="B56" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>137247959</v>
       </c>
       <c r="B57" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137247973</v>
       </c>
       <c r="B58" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>137248057</v>
       </c>
       <c r="B59" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>137248334</v>
       </c>
       <c r="B60" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>137248391</v>
       </c>
       <c r="B61" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>137248441</v>
       </c>
       <c r="B62" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>137248559</v>
       </c>
       <c r="B63" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>137248598</v>
       </c>
       <c r="B64" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>137248605</v>
       </c>
       <c r="B65" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>137248651</v>
       </c>
       <c r="B66" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>137248729</v>
       </c>
       <c r="B67" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>137248753</v>
       </c>
       <c r="B68" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>137248790</v>
       </c>
       <c r="B69" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>137248994</v>
       </c>
       <c r="B70" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>137249072</v>
       </c>
       <c r="B71" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>137249078</v>
       </c>
       <c r="B72" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137249172</v>
       </c>
       <c r="B73" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137249244</v>
       </c>
       <c r="B74" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137249262</v>
       </c>
       <c r="B75" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>137249454</v>
       </c>
       <c r="B76" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>137249472</v>
       </c>
       <c r="B77" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>137249521</v>
       </c>
       <c r="B78" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>137249580</v>
       </c>
       <c r="B79" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>137249647</v>
       </c>
       <c r="B80" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>137249723</v>
       </c>
       <c r="B81" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137249763</v>
       </c>
       <c r="B82" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>137251044</v>
       </c>
       <c r="B83" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>137251050</v>
       </c>
       <c r="B84" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>137251052</v>
       </c>
       <c r="B85" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>137251055</v>
       </c>
       <c r="B86" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>137251056</v>
       </c>
       <c r="B87" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>137251057</v>
       </c>
       <c r="B88" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>137251058</v>
       </c>
       <c r="B89" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>137251061</v>
       </c>
       <c r="B90" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>137251062</v>
       </c>
       <c r="B91" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>137251069</v>
       </c>
       <c r="B92" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>137251075</v>
       </c>
       <c r="B93" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>137251093</v>
       </c>
       <c r="B94" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>137251097</v>
       </c>
       <c r="B95" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>137251120</v>
       </c>
       <c r="B96" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>137251121</v>
       </c>
       <c r="B97" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>137251123</v>
       </c>
       <c r="B98" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>137251129</v>
       </c>
       <c r="B99" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>137251131</v>
       </c>
       <c r="B100" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>137251139</v>
       </c>
       <c r="B101" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>137251143</v>
       </c>
       <c r="B102" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>137251145</v>
       </c>
       <c r="B103" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>137251149</v>
       </c>
       <c r="B104" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>137251157</v>
       </c>
       <c r="B105" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>137251158</v>
       </c>
       <c r="B106" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>137251171</v>
       </c>
       <c r="B107" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>137251173</v>
       </c>
       <c r="B108" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>137251175</v>
       </c>
       <c r="B109" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>137251190</v>
       </c>
       <c r="B110" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>137251199</v>
       </c>
       <c r="B111" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>137251201</v>
       </c>
       <c r="B112" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>137251203</v>
       </c>
       <c r="B113" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>137251204</v>
       </c>
       <c r="B114" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>137251205</v>
       </c>
       <c r="B115" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>137251207</v>
       </c>
       <c r="B116" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>137248899</v>
       </c>
       <c r="B117" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>137247831</v>
       </c>
       <c r="B119" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>137247892</v>
       </c>
       <c r="B120" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>137248816</v>
       </c>
       <c r="B121" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>137251074</v>
       </c>
       <c r="B122" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>137251081</v>
       </c>
       <c r="B123" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>137251085</v>
       </c>
       <c r="B124" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>137251092</v>
       </c>
       <c r="B125" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>137251094</v>
       </c>
       <c r="B126" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>137251098</v>
       </c>
       <c r="B127" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>137251119</v>
       </c>
       <c r="B128" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>137251138</v>
       </c>
       <c r="B129" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>137251156</v>
       </c>
       <c r="B130" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>137251191</v>
       </c>
       <c r="B131" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>137251202</v>
       </c>
       <c r="B132" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>137251048</v>
       </c>
       <c r="B133" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>137251051</v>
       </c>
       <c r="B134" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>137251066</v>
       </c>
       <c r="B135" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>137251070</v>
       </c>
       <c r="B136" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>137251073</v>
       </c>
       <c r="B137" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>137251076</v>
       </c>
       <c r="B138" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>137251080</v>
       </c>
       <c r="B139" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>137251083</v>
       </c>
       <c r="B140" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>137251105</v>
       </c>
       <c r="B141" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>137251107</v>
       </c>
       <c r="B142" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>137251115</v>
       </c>
       <c r="B143" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>137251128</v>
       </c>
       <c r="B144" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>137251137</v>
       </c>
       <c r="B145" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>137251147</v>
       </c>
       <c r="B146" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>137251196</v>
       </c>
       <c r="B147" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>137251206</v>
       </c>
       <c r="B148" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>137248916</v>
       </c>
       <c r="B149" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>137248245</v>
       </c>
       <c r="B152" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>137248415</v>
       </c>
       <c r="B153" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137248504</v>
       </c>
       <c r="B154" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>137248967</v>
       </c>
       <c r="B155" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>137249014</v>
       </c>
       <c r="B156" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>137249156</v>
       </c>
       <c r="B157" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>137249143</v>
       </c>
       <c r="B158" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>137249220</v>
       </c>
       <c r="B159" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>137251188</v>
       </c>
       <c r="B160" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>137247679</v>
       </c>
       <c r="B161" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>137249409</v>
       </c>
       <c r="B162" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>137251067</v>
       </c>
       <c r="B163" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>137251101</v>
       </c>
       <c r="B164" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>137247706</v>
       </c>
       <c r="B165" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>137248269</v>
       </c>
       <c r="B166" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>137248419</v>
       </c>
       <c r="B167" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>137248840</v>
       </c>
       <c r="B168" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>137249022</v>
       </c>
       <c r="B169" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>137249631</v>
       </c>
       <c r="B170" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>137251065</v>
       </c>
       <c r="B171" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>137251088</v>
       </c>
       <c r="B172" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>137251095</v>
       </c>
       <c r="B173" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>137251104</v>
       </c>
       <c r="B174" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>137251112</v>
       </c>
       <c r="B175" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>137251126</v>
       </c>
       <c r="B176" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>137251130</v>
       </c>
       <c r="B177" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>137251132</v>
       </c>
       <c r="B178" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>137251142</v>
       </c>
       <c r="B179" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>137251144</v>
       </c>
       <c r="B180" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>137251150</v>
       </c>
       <c r="B181" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>137251151</v>
       </c>
       <c r="B182" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>137251153</v>
       </c>
       <c r="B183" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>137251170</v>
       </c>
       <c r="B184" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>137251193</v>
       </c>
       <c r="B185" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>137251198</v>
       </c>
       <c r="B186" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>137251077</v>
       </c>
       <c r="B187" t="n">
-        <v>56587</v>
+        <v>56597</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>137251047</v>
       </c>
       <c r="B191" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>137251102</v>
       </c>
       <c r="B192" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>137251109</v>
       </c>
       <c r="B193" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>137251122</v>
       </c>
       <c r="B194" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>137251154</v>
       </c>
       <c r="B195" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>137251096</v>
       </c>
       <c r="B196" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>137251106</v>
       </c>
       <c r="B197" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 33107-2026 artfynd.xlsx
+++ b/artfynd/A 33107-2026 artfynd.xlsx
@@ -3259,7 +3259,7 @@
         <v>137251189</v>
       </c>
       <c r="B25" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>137251064</v>
       </c>
       <c r="B32" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>137251140</v>
       </c>
       <c r="B33" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>137251174</v>
       </c>
       <c r="B34" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>137251127</v>
       </c>
       <c r="B35" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>137249391</v>
       </c>
       <c r="B36" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137251110</v>
       </c>
       <c r="B37" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137251111</v>
       </c>
       <c r="B38" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>137251047</v>
       </c>
       <c r="B191" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>137251102</v>
       </c>
       <c r="B192" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>137251109</v>
       </c>
       <c r="B193" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>137251122</v>
       </c>
       <c r="B194" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>137251154</v>
       </c>
       <c r="B195" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 33107-2026 artfynd.xlsx
+++ b/artfynd/A 33107-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137251049</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137251059</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137251068</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137251072</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137251078</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137251079</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137251084</v>
       </c>
       <c r="B10" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137251090</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137251100</v>
       </c>
       <c r="B12" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137251108</v>
       </c>
       <c r="B13" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137251114</v>
       </c>
       <c r="B14" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137251116</v>
       </c>
       <c r="B15" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137251117</v>
       </c>
       <c r="B16" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137251134</v>
       </c>
       <c r="B17" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137251135</v>
       </c>
       <c r="B18" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137251136</v>
       </c>
       <c r="B19" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137251146</v>
       </c>
       <c r="B20" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137251148</v>
       </c>
       <c r="B21" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137251192</v>
       </c>
       <c r="B22" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137251194</v>
       </c>
       <c r="B23" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137251197</v>
       </c>
       <c r="B24" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137251189</v>
       </c>
       <c r="B25" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137251099</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>79611</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>137251060</v>
       </c>
       <c r="B29" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>137251063</v>
       </c>
       <c r="B30" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>137251064</v>
       </c>
       <c r="B32" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>137251140</v>
       </c>
       <c r="B33" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>137251174</v>
       </c>
       <c r="B34" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>137251127</v>
       </c>
       <c r="B35" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>137249391</v>
       </c>
       <c r="B36" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137251110</v>
       </c>
       <c r="B37" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137251111</v>
       </c>
       <c r="B38" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>137247320</v>
       </c>
       <c r="B49" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>137247343</v>
       </c>
       <c r="B50" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>137247420</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137247486</v>
       </c>
       <c r="B52" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>137247513</v>
       </c>
       <c r="B53" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>137247625</v>
       </c>
       <c r="B54" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>137247711</v>
       </c>
       <c r="B55" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>137247798</v>
       </c>
       <c r="B56" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>137247959</v>
       </c>
       <c r="B57" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137247973</v>
       </c>
       <c r="B58" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>137248057</v>
       </c>
       <c r="B59" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>137248334</v>
       </c>
       <c r="B60" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>137248391</v>
       </c>
       <c r="B61" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>137248441</v>
       </c>
       <c r="B62" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>137248559</v>
       </c>
       <c r="B63" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>137248598</v>
       </c>
       <c r="B64" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>137248605</v>
       </c>
       <c r="B65" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>137248651</v>
       </c>
       <c r="B66" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>137248729</v>
       </c>
       <c r="B67" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>137248753</v>
       </c>
       <c r="B68" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>137248790</v>
       </c>
       <c r="B69" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>137248994</v>
       </c>
       <c r="B70" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>137249072</v>
       </c>
       <c r="B71" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>137249078</v>
       </c>
       <c r="B72" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137249172</v>
       </c>
       <c r="B73" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137249244</v>
       </c>
       <c r="B74" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137249262</v>
       </c>
       <c r="B75" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>137249454</v>
       </c>
       <c r="B76" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>137249472</v>
       </c>
       <c r="B77" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>137249521</v>
       </c>
       <c r="B78" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>137249580</v>
       </c>
       <c r="B79" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>137249647</v>
       </c>
       <c r="B80" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>137249723</v>
       </c>
       <c r="B81" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137249763</v>
       </c>
       <c r="B82" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>137251044</v>
       </c>
       <c r="B83" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>137251050</v>
       </c>
       <c r="B84" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>137251052</v>
       </c>
       <c r="B85" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>137251055</v>
       </c>
       <c r="B86" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>137251056</v>
       </c>
       <c r="B87" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>137251057</v>
       </c>
       <c r="B88" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>137251058</v>
       </c>
       <c r="B89" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>137251061</v>
       </c>
       <c r="B90" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>137251062</v>
       </c>
       <c r="B91" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>137251069</v>
       </c>
       <c r="B92" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>137251075</v>
       </c>
       <c r="B93" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>137251093</v>
       </c>
       <c r="B94" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>137251097</v>
       </c>
       <c r="B95" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>137251120</v>
       </c>
       <c r="B96" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>137251121</v>
       </c>
       <c r="B97" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>137251123</v>
       </c>
       <c r="B98" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>137251129</v>
       </c>
       <c r="B99" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>137251131</v>
       </c>
       <c r="B100" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>137251139</v>
       </c>
       <c r="B101" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>137251143</v>
       </c>
       <c r="B102" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>137251145</v>
       </c>
       <c r="B103" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>137251149</v>
       </c>
       <c r="B104" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>137251157</v>
       </c>
       <c r="B105" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>137251158</v>
       </c>
       <c r="B106" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>137251171</v>
       </c>
       <c r="B107" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>137251173</v>
       </c>
       <c r="B108" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>137251175</v>
       </c>
       <c r="B109" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>137251190</v>
       </c>
       <c r="B110" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>137251199</v>
       </c>
       <c r="B111" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>137251201</v>
       </c>
       <c r="B112" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>137251203</v>
       </c>
       <c r="B113" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>137251204</v>
       </c>
       <c r="B114" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>137251205</v>
       </c>
       <c r="B115" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>137251207</v>
       </c>
       <c r="B116" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>137248899</v>
       </c>
       <c r="B117" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>137247831</v>
       </c>
       <c r="B119" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>137247892</v>
       </c>
       <c r="B120" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>137248816</v>
       </c>
       <c r="B121" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>137251074</v>
       </c>
       <c r="B122" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>137251081</v>
       </c>
       <c r="B123" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>137251085</v>
       </c>
       <c r="B124" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>137251092</v>
       </c>
       <c r="B125" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>137251094</v>
       </c>
       <c r="B126" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>137251098</v>
       </c>
       <c r="B127" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>137251119</v>
       </c>
       <c r="B128" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>137251138</v>
       </c>
       <c r="B129" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>137251156</v>
       </c>
       <c r="B130" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>137251191</v>
       </c>
       <c r="B131" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>137251202</v>
       </c>
       <c r="B132" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>137251048</v>
       </c>
       <c r="B133" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>137251051</v>
       </c>
       <c r="B134" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>137251066</v>
       </c>
       <c r="B135" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>137251070</v>
       </c>
       <c r="B136" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>137251073</v>
       </c>
       <c r="B137" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>137251076</v>
       </c>
       <c r="B138" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>137251080</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>137251083</v>
       </c>
       <c r="B140" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>137251105</v>
       </c>
       <c r="B141" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>137251107</v>
       </c>
       <c r="B142" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>137251115</v>
       </c>
       <c r="B143" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>137251128</v>
       </c>
       <c r="B144" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>137251137</v>
       </c>
       <c r="B145" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>137251147</v>
       </c>
       <c r="B146" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>137251196</v>
       </c>
       <c r="B147" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>137251206</v>
       </c>
       <c r="B148" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>137248916</v>
       </c>
       <c r="B149" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>137248245</v>
       </c>
       <c r="B152" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>137248415</v>
       </c>
       <c r="B153" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137248504</v>
       </c>
       <c r="B154" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>137248967</v>
       </c>
       <c r="B155" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>137249014</v>
       </c>
       <c r="B156" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>137249156</v>
       </c>
       <c r="B157" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>137249143</v>
       </c>
       <c r="B158" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>137249220</v>
       </c>
       <c r="B159" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>137251188</v>
       </c>
       <c r="B160" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>137247679</v>
       </c>
       <c r="B161" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>137249409</v>
       </c>
       <c r="B162" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>137251067</v>
       </c>
       <c r="B163" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>137251101</v>
       </c>
       <c r="B164" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>137251077</v>
       </c>
       <c r="B187" t="n">
-        <v>56597</v>
+        <v>56598</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>137251047</v>
       </c>
       <c r="B191" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>137251102</v>
       </c>
       <c r="B192" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>137251109</v>
       </c>
       <c r="B193" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>137251122</v>
       </c>
       <c r="B194" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>137251154</v>
       </c>
       <c r="B195" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>137251096</v>
       </c>
       <c r="B196" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>137251106</v>
       </c>
       <c r="B197" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
